--- a/docs/YHG_ユーザーマニュアル.xlsx
+++ b/docs/YHG_ユーザーマニュアル.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,24 +38,24 @@
       <name val="MS ゴシック"/>
       <b val="1"/>
       <color rgb="001F4E78"/>
-      <sz val="56"/>
+      <sz val="28"/>
     </font>
     <font>
       <name val="MS ゴシック"/>
       <b val="1"/>
       <color rgb="002E75B6"/>
-      <sz val="30"/>
+      <sz val="22"/>
     </font>
     <font>
       <name val="MS ゴシック"/>
       <color rgb="00555555"/>
-      <sz val="16"/>
+      <sz val="18"/>
     </font>
     <font>
       <name val="MS ゴシック"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <sz val="15"/>
     </font>
     <font>
       <name val="MS ゴシック"/>
@@ -105,36 +105,18 @@
     <font>
       <name val="MS ゴシック"/>
       <b val="1"/>
-      <color rgb="00B91C1C"/>
-      <sz val="12"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
     </font>
     <font>
       <name val="MS ゴシック"/>
       <b val="1"/>
-      <color rgb="007C3AED"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="MS ゴシック"/>
-      <b val="1"/>
-      <color rgb="00047857"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="MS ゴシック"/>
-      <b val="1"/>
-      <color rgb="006B7280"/>
+      <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Consolas"/>
       <color rgb="001F4E78"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="MS ゴシック"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -177,6 +159,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00B91C1C"/>
       </patternFill>
     </fill>
@@ -193,11 +180,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="006B7280"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -247,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -288,7 +270,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -297,30 +279,30 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -337,16 +319,10 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -437,10 +413,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9048750" cy="4371975"/>
+    <ext cx="9334500" cy="6562725"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -448,6 +424,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9334500" cy="6562725"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -470,7 +471,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9048750" cy="4371975"/>
+    <ext cx="9334500" cy="6562725"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -497,10 +498,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>4</row>
+      <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9048750" cy="6705600"/>
+    <ext cx="10477500" cy="5181600"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -508,6 +509,31 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>37</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="10477500" cy="2009775"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -530,7 +556,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="9048750" cy="5248275"/>
+    <ext cx="10477500" cy="4591050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -557,40 +583,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6667500" cy="4000500"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>8</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9048750" cy="2038350"/>
+    <ext cx="10477500" cy="7362825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -911,35 +907,35 @@
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1"/>
-    <row r="3" ht="84" customHeight="1">
+    <row r="3" ht="50" customHeight="1">
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>YHG</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="50" customHeight="1">
+          <t>構造図・計算書 整合チェックツール</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>ユーザーマニュアル</t>
+          <t>（RC小梁・スラブ）</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>構造図・計算書 整合チェックツール</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+          <t>ユーザーマニュアル</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
           <t>3 ステップで完了</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="72" customHeight="1">
+    <row r="9" ht="64" customHeight="1">
       <c r="B9" s="5" t="inlineStr">
         <is>
           <t>STEP 1
@@ -965,15 +961,15 @@
     <row r="11" ht="24" customHeight="1">
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>動作環境</t>
+          <t>起動方法</t>
         </is>
       </c>
     </row>
     <row r="12" ht="50" customHeight="1">
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>・Windows PC（YHG.exe を実行）
-・ブラウザは内蔵 — 別途インストール不要</t>
+          <t>整合チェックツール(RC小梁・スラブ).exe をダブルクリックで起動。
+ブラウザは内蔵 — 別途インストール不要。</t>
         </is>
       </c>
     </row>
@@ -1052,14 +1048,14 @@
       </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="36" t="inlineStr">
+      <c r="A3" s="34" t="inlineStr">
         <is>
           <t>Q. PDF抽出ができないと言われる</t>
         </is>
       </c>
     </row>
     <row r="4" ht="50" customHeight="1">
-      <c r="A4" s="37" t="inlineStr">
+      <c r="A4" s="35" t="inlineStr">
         <is>
           <t>図面 PDF が SHX フォントまたは画像 PDF の可能性。
 → シート「6. PDF形式の注意」「7. AutoCAD手順」を参照。</t>
@@ -1067,29 +1063,29 @@
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="36" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>Q. 大量の「計算書のみ」が出る</t>
         </is>
       </c>
     </row>
     <row r="7" ht="50" customHeight="1">
-      <c r="A7" s="37" t="inlineStr">
-        <is>
-          <t>基礎梁リストが計算書のみで構造図に無い等の可能性。
-→ 基礎梁リスト PDF を追加投入、または「基礎部材を除外」フィルタ ON。</t>
+      <c r="A7" s="35" t="inlineStr">
+        <is>
+          <t>基礎梁系（FB/FCG/FG）が計算書にあるが構造図に基礎梁リストが無い等の可能性。
+→ 基礎梁リスト PDF を追加投入、または「基礎部材を除外」フィルタを ON。</t>
         </is>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="36" t="inlineStr">
+      <c r="A9" s="34" t="inlineStr">
         <is>
           <t>Q. 「配筋不一致」が出るが図面と計算書を見比べると合っている</t>
         </is>
       </c>
     </row>
     <row r="10" ht="90" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="35" t="inlineStr">
         <is>
           <t>・同符号で複数断面（B2 が階により異なる等）→ 図面で枝番化を検討
 ・計算書注記による上書きを見落とし
@@ -1099,47 +1095,47 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1">
-      <c r="A12" s="36" t="inlineStr">
-        <is>
-          <t>Q. 「要目視確認」が増えた</t>
+      <c r="A12" s="34" t="inlineStr">
+        <is>
+          <t>Q. 「要目視確認」が出るケース</t>
         </is>
       </c>
     </row>
     <row r="13" ht="110" customHeight="1">
-      <c r="A13" s="37" t="inlineStr">
-        <is>
-          <t>下記いずれかに該当：
+      <c r="A13" s="35" t="inlineStr">
+        <is>
+          <t>下記のいずれか：
 ・連梁（通り芯ごとに配筋が異なる）
 ・構造図の全断面値が計算書の複数バリアントを包絡
-・同符号で計算書に複数検討あり
-→ 計算書を目視確認し、必要なら図面に補足記載。</t>
+・同符号で計算書に複数検討あり、かつ いずれかで端部・中央 等で配筋が違う
+→「PDFで照合」で計算書を目視確認。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1">
-      <c r="A15" s="36" t="inlineStr">
+      <c r="A15" s="34" t="inlineStr">
         <is>
           <t>Q. 整合チェックが遅い</t>
         </is>
       </c>
     </row>
     <row r="16" ht="50" customHeight="1">
-      <c r="A16" s="37" t="inlineStr">
-        <is>
-          <t>計算書が 50 ページ超／複数ファイル同時投入の場合は 1 分前後かかります。
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>計算書が 50 ページ超／複数ファイル同時投入の場合 1 分前後かかります。
 1 分以上止まる場合は再起動して再試行。</t>
         </is>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="36" t="inlineStr">
+      <c r="A18" s="34" t="inlineStr">
         <is>
           <t>Q. 「PDFで照合」モーダルで画像が出ない</t>
         </is>
       </c>
     </row>
     <row r="19" ht="50" customHeight="1">
-      <c r="A19" s="37" t="inlineStr">
+      <c r="A19" s="35" t="inlineStr">
         <is>
           <t>ブラウザキャッシュやアップロード直後に発生することがあります。
 → モーダルを閉じて再度開く／「すべて消去」→ 再投入 → 再実行。</t>
@@ -1153,10 +1149,11 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="42" customHeight="1">
-      <c r="A22" s="38" t="inlineStr">
-        <is>
-          <t>2026.06.10 スクリーンショット中心の構成にリニューアル
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="36" t="inlineStr">
+        <is>
+          <t>・実画面スクリーンショットを使用したマニュアルにリニューアル
+・exe 名を「整合チェックツール(RC小梁・スラブ).exe」に変更
 ツールの不具合・改善要望は開発担当までご連絡ください。</t>
         </is>
       </c>
@@ -1233,7 +1230,7 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>起動～PDF投入</t>
+          <t>起動 〜 PDF 投入</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
@@ -1318,7 +1315,7 @@
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>図面PDFの形式（最重要）</t>
+          <t>図面 PDF の形式（最重要）</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
@@ -1387,7 +1384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L28"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1407,39 +1404,27 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>1. 起動 ～ PDF を投入</t>
+          <t>1. 起動 〜 PDF を投入</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STEP 1　YHG.exe を起動</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
+          <t xml:space="preserve">  STEP 1　整合チェックツール(RC小梁・スラブ).exe を起動</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="15" t="inlineStr">
         <is>
-          <t>ダブルクリックで起動。ブラウザ画面が自動で開きます（別途ブラウザを開く必要はありません）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STEP 2　構造図 PDF と計算書 PDF をドラッグ＆ドロップ</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>左：構造図（小梁リスト・スラブリスト・基礎梁リスト等）／右：計算書（小梁編・スラブ編）。複数ファイル可。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="6" customHeight="1"/>
+          <t>ダブルクリックで起動。ブラウザが自動で開きます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1"/>
+    <row r="7" ht="22" customHeight="1"/>
+    <row r="8" ht="22" customHeight="1"/>
     <row r="9" ht="22" customHeight="1"/>
     <row r="10" ht="22" customHeight="1"/>
     <row r="11" ht="22" customHeight="1"/>
@@ -1459,19 +1444,72 @@
     <row r="25" ht="22" customHeight="1"/>
     <row r="26" ht="22" customHeight="1"/>
     <row r="27" ht="22" customHeight="1"/>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>✅ 構造図と計算書を両方入れた時点で「整合チェック実行」ボタンが青く有効になります。</t>
+    <row r="28" ht="22" customHeight="1"/>
+    <row r="29" ht="22" customHeight="1"/>
+    <row r="30" ht="22" customHeight="1"/>
+    <row r="31" ht="22" customHeight="1"/>
+    <row r="32" ht="22" customHeight="1"/>
+    <row r="33" ht="22" customHeight="1"/>
+    <row r="34" ht="22" customHeight="1"/>
+    <row r="35" ht="22" customHeight="1"/>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STEP 2　構造図 PDF と計算書 PDF をそれぞれの枠に投入</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="42" customHeight="1">
+      <c r="A38" s="15" t="inlineStr">
+        <is>
+          <t>左：構造図（二次部材リスト）／右：計算書（小梁計算書・スラブ計算書）。
+ドラッグ＆ドロップでもクリック選択でも可。複数ファイル投入も可能。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1"/>
+    <row r="41" ht="22" customHeight="1"/>
+    <row r="42" ht="22" customHeight="1"/>
+    <row r="43" ht="22" customHeight="1"/>
+    <row r="44" ht="22" customHeight="1"/>
+    <row r="45" ht="22" customHeight="1"/>
+    <row r="46" ht="22" customHeight="1"/>
+    <row r="47" ht="22" customHeight="1"/>
+    <row r="48" ht="22" customHeight="1"/>
+    <row r="49" ht="22" customHeight="1"/>
+    <row r="50" ht="22" customHeight="1"/>
+    <row r="51" ht="22" customHeight="1"/>
+    <row r="52" ht="22" customHeight="1"/>
+    <row r="53" ht="22" customHeight="1"/>
+    <row r="54" ht="22" customHeight="1"/>
+    <row r="55" ht="22" customHeight="1"/>
+    <row r="56" ht="22" customHeight="1"/>
+    <row r="57" ht="22" customHeight="1"/>
+    <row r="58" ht="22" customHeight="1"/>
+    <row r="59" ht="22" customHeight="1"/>
+    <row r="60" ht="22" customHeight="1"/>
+    <row r="61" ht="22" customHeight="1"/>
+    <row r="62" ht="22" customHeight="1"/>
+    <row r="63" ht="22" customHeight="1"/>
+    <row r="64" ht="22" customHeight="1"/>
+    <row r="65" ht="22" customHeight="1"/>
+    <row r="66" ht="22" customHeight="1"/>
+    <row r="67" ht="22" customHeight="1"/>
+    <row r="68" ht="22" customHeight="1"/>
+    <row r="69" ht="22" customHeight="1"/>
+    <row r="71" ht="28" customHeight="1">
+      <c r="A71" s="16" t="inlineStr">
+        <is>
+          <t>✅ 両方の枠にファイルが入ると「整合チェック実行」ボタンが青く有効になります。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A7:L7"/>
+    <mergeCell ref="A38:L38"/>
+    <mergeCell ref="A71:L71"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A37:L37"/>
     <mergeCell ref="A3:L3"/>
     <mergeCell ref="A4:L4"/>
   </mergeCells>
@@ -1488,7 +1526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1515,14 +1553,15 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STEP 1　ファイル投入後、ボタンが有効化される</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
+          <t xml:space="preserve">  STEP 1　「整合チェック実行」ボタンをクリック</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
       <c r="A4" s="15" t="inlineStr">
         <is>
-          <t>両方のドロップエリアにファイルが入ると「整合チェック実行」が押せるようになります。</t>
+          <t>通常 20〜60 秒で結果が表示されます。
+計算書 PDF のページ数が多い場合は 1 分前後かかることがあります。</t>
         </is>
       </c>
     </row>
@@ -1544,28 +1583,31 @@
     <row r="21" ht="22" customHeight="1"/>
     <row r="22" ht="22" customHeight="1"/>
     <row r="23" ht="22" customHeight="1"/>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STEP 2　クリックして待つ（通常 20〜60 秒）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="46" customHeight="1">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>計算書 PDF のページ数に比例して処理時間が変わります。
-50 ページを超える計算書や複数ファイルを同時投入した場合は 1 分前後かかることがあります。</t>
+    <row r="24" ht="22" customHeight="1"/>
+    <row r="25" ht="22" customHeight="1"/>
+    <row r="26" ht="22" customHeight="1"/>
+    <row r="27" ht="22" customHeight="1"/>
+    <row r="28" ht="22" customHeight="1"/>
+    <row r="29" ht="22" customHeight="1"/>
+    <row r="30" ht="22" customHeight="1"/>
+    <row r="31" ht="22" customHeight="1"/>
+    <row r="32" ht="22" customHeight="1"/>
+    <row r="33" ht="22" customHeight="1"/>
+    <row r="34" ht="22" customHeight="1"/>
+    <row r="35" ht="22" customHeight="1"/>
+    <row r="37" ht="28" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>実行中は画面下に進捗が表示されます。完了すると下に小梁・スラブの結果カードが表示されます。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A26:L26"/>
+  <mergeCells count="4">
+    <mergeCell ref="A3:L3"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A27:L27"/>
-    <mergeCell ref="A3:L3"/>
     <mergeCell ref="A4:L4"/>
+    <mergeCell ref="A37:L37"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -1580,7 +1622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1604,10 +1646,323 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="42" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>結果テーブルは「符号 ＋ 判定 ＋ 配筋値 ＋ 操作（PDFで照合）」で構成されます。判定の色で重要度が一目で分かります。</t>
+          <t>結果は「小梁」と「スラブ」のカードで分かれて表示されます。
+判定の色と「PDFで照合」ボタンで効率よく目視確認できます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STEP 小梁　整合チェック結果（小梁）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1"/>
+    <row r="7" ht="22" customHeight="1"/>
+    <row r="8" ht="22" customHeight="1"/>
+    <row r="9" ht="22" customHeight="1"/>
+    <row r="10" ht="22" customHeight="1"/>
+    <row r="11" ht="22" customHeight="1"/>
+    <row r="12" ht="22" customHeight="1"/>
+    <row r="13" ht="22" customHeight="1"/>
+    <row r="14" ht="22" customHeight="1"/>
+    <row r="15" ht="22" customHeight="1"/>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="19" ht="22" customHeight="1"/>
+    <row r="20" ht="22" customHeight="1"/>
+    <row r="21" ht="22" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1"/>
+    <row r="23" ht="22" customHeight="1"/>
+    <row r="24" ht="22" customHeight="1"/>
+    <row r="25" ht="22" customHeight="1"/>
+    <row r="26" ht="22" customHeight="1"/>
+    <row r="27" ht="22" customHeight="1"/>
+    <row r="28" ht="22" customHeight="1"/>
+    <row r="29" ht="22" customHeight="1"/>
+    <row r="30" ht="22" customHeight="1"/>
+    <row r="31" ht="22" customHeight="1"/>
+    <row r="32" ht="22" customHeight="1"/>
+    <row r="33" ht="22" customHeight="1"/>
+    <row r="34" ht="22" customHeight="1"/>
+    <row r="35" ht="22" customHeight="1"/>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STEP スラブ　整合チェック結果（スラブ）</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1"/>
+    <row r="39" ht="22" customHeight="1"/>
+    <row r="40" ht="22" customHeight="1"/>
+    <row r="41" ht="22" customHeight="1"/>
+    <row r="42" ht="22" customHeight="1"/>
+    <row r="43" ht="22" customHeight="1"/>
+    <row r="44" ht="22" customHeight="1"/>
+    <row r="45" ht="22" customHeight="1"/>
+    <row r="46" ht="22" customHeight="1"/>
+    <row r="47" ht="22" customHeight="1"/>
+    <row r="48" ht="22" customHeight="1"/>
+    <row r="49" ht="22" customHeight="1"/>
+    <row r="50" ht="22" customHeight="1"/>
+    <row r="51" ht="22" customHeight="1"/>
+    <row r="52" ht="22" customHeight="1"/>
+    <row r="53" ht="22" customHeight="1"/>
+    <row r="54" ht="22" customHeight="1"/>
+    <row r="55" ht="22" customHeight="1"/>
+    <row r="56" ht="22" customHeight="1"/>
+    <row r="57" ht="22" customHeight="1"/>
+    <row r="58" ht="22" customHeight="1"/>
+    <row r="59" ht="22" customHeight="1"/>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>判定の色凡例</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="19" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="B62" s="20" t="inlineStr">
+        <is>
+          <t>配筋不一致／断面幅不一致</t>
+        </is>
+      </c>
+      <c r="E62" s="21" t="inlineStr">
+        <is>
+          <t>図面と計算書で値が異なる。設計者確認が必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="B63" s="23" t="inlineStr">
+        <is>
+          <t>要目視確認</t>
+        </is>
+      </c>
+      <c r="E63" s="21" t="inlineStr">
+        <is>
+          <t>連梁・複数検討・包絡記載など。PDFで照合して目視確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="24" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="B64" s="25" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="E64" s="21" t="inlineStr">
+        <is>
+          <t>対応不要（既定で非表示）</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="26" t="inlineStr">
+        <is>
+          <t>　</t>
+        </is>
+      </c>
+      <c r="B65" s="27" t="inlineStr">
+        <is>
+          <t>計算書のみ／構造図のみ</t>
+        </is>
+      </c>
+      <c r="E65" s="21" t="inlineStr">
+        <is>
+          <t>片側にしか存在しない符号</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="18" t="inlineStr">
+        <is>
+          <t>フィルタ</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="68" customHeight="1">
+      <c r="A68" s="15" t="inlineStr">
+        <is>
+          <t>・基礎部材（FB/FCG/FG）／片持小梁（CB/WCB）／壁梁（WB）を一括非表示にできます。
+・判定種別（配筋不一致・要目視確認 等）のチェックボックスで表示／非表示を切替。
+・「表示中の項目のみ出力」をONにすると、PDFレポートも現在の表示状態に絞り込めます。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="E64:L64"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="A68:L68"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A37:L37"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="E63:L63"/>
+    <mergeCell ref="E62:L62"/>
+    <mergeCell ref="A61:L61"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="A67:L67"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="E65:L65"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="3" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>4. PDFで照合（差分を画像で目視）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="46" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>結果テーブルの「PDFで照合」ボタンを押すと、構造図と計算書の該当箇所が並んで開きます。
+橙枠＝部材全体／赤枠＝差分行 でハイライトされます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1"/>
+    <row r="7" ht="22" customHeight="1"/>
+    <row r="8" ht="22" customHeight="1"/>
+    <row r="9" ht="22" customHeight="1"/>
+    <row r="10" ht="22" customHeight="1"/>
+    <row r="11" ht="22" customHeight="1"/>
+    <row r="12" ht="22" customHeight="1"/>
+    <row r="13" ht="22" customHeight="1"/>
+    <row r="14" ht="22" customHeight="1"/>
+    <row r="15" ht="22" customHeight="1"/>
+    <row r="16" ht="22" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1"/>
+    <row r="18" ht="22" customHeight="1"/>
+    <row r="19" ht="22" customHeight="1"/>
+    <row r="20" ht="22" customHeight="1"/>
+    <row r="21" ht="22" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1"/>
+    <row r="23" ht="22" customHeight="1"/>
+    <row r="24" ht="22" customHeight="1"/>
+    <row r="25" ht="22" customHeight="1"/>
+    <row r="26" ht="22" customHeight="1"/>
+    <row r="27" ht="22" customHeight="1"/>
+    <row r="28" ht="22" customHeight="1"/>
+    <row r="29" ht="22" customHeight="1"/>
+    <row r="30" ht="22" customHeight="1"/>
+    <row r="31" ht="22" customHeight="1"/>
+    <row r="32" ht="22" customHeight="1"/>
+    <row r="33" ht="22" customHeight="1"/>
+    <row r="34" ht="22" customHeight="1"/>
+    <row r="35" ht="22" customHeight="1"/>
+    <row r="36" ht="22" customHeight="1"/>
+    <row r="37" ht="22" customHeight="1"/>
+    <row r="38" ht="22" customHeight="1"/>
+    <row r="39" ht="22" customHeight="1"/>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>ヒント：閉じるは右上「閉じる」ボタン。画像が出ない場合は一度閉じて再度開くか、
+「すべて消去」→ ファイル再アップロード → 整合チェック再実行をお試しください。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:L41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="3" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="42" customHeight="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>5. PDF レポート出力</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>結果カード右上の「小梁をPDF出力」「スラブをPDF出力」で、差分箇所を 1 冊にまとめた PDF を保存できます。</t>
         </is>
       </c>
     </row>
@@ -1645,112 +2000,21 @@
     <row r="36" ht="22" customHeight="1"/>
     <row r="37" ht="22" customHeight="1"/>
     <row r="38" ht="22" customHeight="1"/>
-    <row r="40" ht="24" customHeight="1">
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>判定の色凡例</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1">
-      <c r="B41" s="18" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="C41" s="19" t="inlineStr">
-        <is>
-          <t>配筋不一致／断面幅不一致</t>
-        </is>
-      </c>
-      <c r="F41" s="20" t="inlineStr">
-        <is>
-          <t>設計者確認が必要</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1">
-      <c r="B42" s="21" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="C42" s="22" t="inlineStr">
-        <is>
-          <t>要目視確認</t>
-        </is>
-      </c>
-      <c r="F42" s="20" t="inlineStr">
-        <is>
-          <t>連梁・複数検討・包絡記載など。PDFで照合して目視確認</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="24" customHeight="1">
-      <c r="B43" s="23" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="C43" s="24" t="inlineStr">
-        <is>
-          <t>一致</t>
-        </is>
-      </c>
-      <c r="F43" s="20" t="inlineStr">
-        <is>
-          <t>対応不要（既定で非表示）</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="24" customHeight="1">
-      <c r="B44" s="25" t="inlineStr">
-        <is>
-          <t>　</t>
-        </is>
-      </c>
-      <c r="C44" s="26" t="inlineStr">
-        <is>
-          <t>計算書のみ／構造図のみ</t>
-        </is>
-      </c>
-      <c r="F44" s="20" t="inlineStr">
-        <is>
-          <t>片側にしか存在しない符号</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="24" customHeight="1">
-      <c r="B46" s="17" t="inlineStr">
-        <is>
-          <t>フィルタ</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="68" customHeight="1">
-      <c r="A47" s="15" t="inlineStr">
-        <is>
-          <t>・基礎部材（FB/FCG/FG）／片持小梁（CB/WCB）／壁梁（WB）を一括非表示にできます。
-・判定種別（配筋不一致・要目視確認 等）ごとに表示／非表示を切替。
-・フィルタ状態は PDF レポート出力にも反映されます（チェックボックスで切替可）。</t>
+    <row r="39" ht="22" customHeight="1"/>
+    <row r="41" ht="54" customHeight="1">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>・各差分について構造図と計算書を見開きで横並びに表示
+・部材全体は橙枠、差分行は赤枠でハイライト
+・元 PDF のページ番号を併記</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="F41:L41"/>
-    <mergeCell ref="A47:L47"/>
+  <mergeCells count="3">
+    <mergeCell ref="A41:L41"/>
+    <mergeCell ref="A3:L3"/>
     <mergeCell ref="A1:L1"/>
-    <mergeCell ref="F44:L44"/>
-    <mergeCell ref="F43:L43"/>
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="F42:L42"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
@@ -1759,13 +2023,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1785,70 +2049,89 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>4. PDFで照合（差分を画像で目視）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="46" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>結果テーブルの「PDFで照合」ボタンを押すと、構造図と計算書の該当箇所を画像で並べて確認できます。
-橙枠＝部材全体、赤枠＝差分箇所。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1"/>
-    <row r="7" ht="22" customHeight="1"/>
-    <row r="8" ht="22" customHeight="1"/>
-    <row r="9" ht="22" customHeight="1"/>
-    <row r="10" ht="22" customHeight="1"/>
-    <row r="11" ht="22" customHeight="1"/>
-    <row r="12" ht="22" customHeight="1"/>
-    <row r="13" ht="22" customHeight="1"/>
-    <row r="14" ht="22" customHeight="1"/>
-    <row r="15" ht="22" customHeight="1"/>
-    <row r="16" ht="22" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1"/>
-    <row r="19" ht="22" customHeight="1"/>
-    <row r="20" ht="22" customHeight="1"/>
-    <row r="21" ht="22" customHeight="1"/>
-    <row r="22" ht="22" customHeight="1"/>
-    <row r="23" ht="22" customHeight="1"/>
-    <row r="24" ht="22" customHeight="1"/>
-    <row r="25" ht="22" customHeight="1"/>
-    <row r="26" ht="22" customHeight="1"/>
-    <row r="27" ht="22" customHeight="1"/>
-    <row r="28" ht="22" customHeight="1"/>
-    <row r="29" ht="22" customHeight="1"/>
-    <row r="31" ht="36" customHeight="1">
-      <c r="A31" s="27" t="inlineStr">
-        <is>
-          <t>ヒント: モーダルが開かない／画像が出ないときは、一度モーダルを閉じて再度開く。
-それでも出ない場合は「すべて消去」→ ファイル再アップロード → 整合チェック再実行。</t>
+          <t>6. 図面 PDF の形式について（最重要）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="28" t="inlineStr">
+        <is>
+          <t>⚠ 本ツールは PDF 内の「文字情報（テキストレイヤー）」を読み取ります。
+  以下の PDF は利用できません。トラブルの大半はこの問題が原因です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>❌ 利用できない PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="62" customHeight="1">
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>・スキャナで紙図面を読み取った PDF（画像のみ）
+・DocuWorks / CubePDF 経由で「SHX フォント」の図面を PDF 化したもの
+・AutoCAD で「SHX フォント」を使ったまま PDF 出力したもの → §7 で対処</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>✅ 重要な例外：TrueType フォントなら DocuWorks / CubePDF 経由も OK</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="62" customHeight="1">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>AutoCAD の文字スタイルが TrueType（MSゴシック・MS明朝・游ゴシック等）なら、
+どの経路で PDF 化しても文字情報が保持されます。
+「DocuWorks 経由は使えない」と言われるのはフォントが SHX の場合のみです。</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  STEP 判別　Ctrl + F で「FG1」等の符号を検索</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>ヒットすれば OK ／ ヒットしなければ画像 PDF（NG）。
+文字をマウスでドラッグして選択できれば OK。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="8">
+    <mergeCell ref="A11:L11"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A5:L5"/>
+    <mergeCell ref="A8:L8"/>
+    <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A9:L9"/>
     <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A12:L12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1868,228 +2151,20 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>5. PDF レポート出力</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="46" customHeight="1">
+          <t>7. AutoCAD から検索可能 PDF を作成する</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="32" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>「小梁をPDF出力」「スラブをPDF出力」ボタンで、差分箇所を 1 冊の PDF にまとめて保存できます。
-社内回覧・是正会議・記録保存に。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1"/>
-    <row r="7" ht="22" customHeight="1"/>
-    <row r="8" ht="22" customHeight="1"/>
-    <row r="9" ht="22" customHeight="1"/>
-    <row r="10" ht="22" customHeight="1"/>
-    <row r="11" ht="22" customHeight="1"/>
-    <row r="12" ht="22" customHeight="1"/>
-    <row r="13" ht="22" customHeight="1"/>
-    <row r="14" ht="22" customHeight="1"/>
-    <row r="15" ht="22" customHeight="1"/>
-    <row r="16" ht="22" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1"/>
-    <row r="19" ht="22" customHeight="1"/>
-    <row r="20" ht="22" customHeight="1"/>
-    <row r="21" ht="22" customHeight="1"/>
-    <row r="22" ht="22" customHeight="1"/>
-    <row r="23" ht="22" customHeight="1"/>
-    <row r="24" ht="22" customHeight="1"/>
-    <row r="25" ht="22" customHeight="1"/>
-    <row r="26" ht="22" customHeight="1"/>
-    <row r="27" ht="22" customHeight="1"/>
-    <row r="29" ht="54" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>・各差分について 構造図と計算書を見開きで横並びに表示
-・部材全体は橙枠、差分行は赤枠でハイライト
-・元 PDF のページ番号を併記（差分箇所への遡及確認が容易）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A29:L29"/>
-    <mergeCell ref="A1:L1"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="3" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="42" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>6. 図面PDFの形式について（最重要）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="28" t="inlineStr">
-        <is>
-          <t>⚠ 本ツールは PDF 内の「文字情報（テキストレイヤー）」を読み取ります。
-  以下に該当する PDF は利用できません。トラブルの大半はこの問題が原因です。</t>
+          <t>AutoCAD で SHX フォントの図面を PDF 出力する場合の対処。下記いずれか 1 つで本ツールが読めるようになります。</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  STEP 1　判別：Ctrl + F で「FG1」等の符号を検索</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>ヒットすれば OK ／ ヒットしなければ画像 PDF（NG）。文字をマウスでドラッグして選択できれば OK。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STEP 2　警告メッセージが出たら §7 AutoCAD手順 へ</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="22" customHeight="1"/>
-    <row r="10" ht="22" customHeight="1"/>
-    <row r="11" ht="22" customHeight="1"/>
-    <row r="12" ht="22" customHeight="1"/>
-    <row r="13" ht="22" customHeight="1"/>
-    <row r="14" ht="22" customHeight="1"/>
-    <row r="15" ht="22" customHeight="1"/>
-    <row r="16" ht="22" customHeight="1"/>
-    <row r="17" ht="22" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1"/>
-    <row r="19" ht="22" customHeight="1"/>
-    <row r="20" ht="22" customHeight="1"/>
-    <row r="21" ht="22" customHeight="1"/>
-    <row r="22" ht="22" customHeight="1"/>
-    <row r="23" ht="22" customHeight="1"/>
-    <row r="24" ht="22" customHeight="1"/>
-    <row r="27" ht="24" customHeight="1">
-      <c r="B27" s="29" t="inlineStr">
-        <is>
-          <t>❌ 利用できない PDF</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="62" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
-        <is>
-          <t>・スキャナで紙図面を読み取った PDF（画像のみ）
-・DocuWorks / CubePDF 経由で「SHX フォント」の図面を PDF 化したもの
-・AutoCAD で「SHX フォント」を使ったまま PDF 出力したもの → §7 で対処</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1">
-      <c r="B30" s="31" t="inlineStr">
-        <is>
-          <t>✅ 重要な例外：TrueType フォントなら DocuWorks 経由も CubePDF 経由もOK</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="62" customHeight="1">
-      <c r="A31" s="32" t="inlineStr">
-        <is>
-          <t>AutoCAD の文字スタイルが TrueType（MSゴシック・MS明朝・游ゴシック等）なら、
-AutoCAD 直接 PDF / DocuWorks 経由 / CubePDF 経由のいずれでも文字情報が保持されます。
-「DocuWorks 経由は使えない」と言われるのはフォントが SHX の場合のみです。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="B30:L30"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A5:L5"/>
-    <mergeCell ref="A28:L28"/>
-    <mergeCell ref="A8:L8"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A6:L6"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="B27:L27"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:L19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="3" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="42" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
-        <is>
-          <t>7. AutoCAD から検索可能 PDF を作成する</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>AutoCAD で SHX フォントを使った図面を PDF 出力する場合の対処。下記いずれか1つで本ツールが読めるようになります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
           <t xml:space="preserve">  STEP 1　PDFSHX 変数を 1 にする（最も簡単）</t>
         </is>
       </c>
@@ -2109,30 +2184,23 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>その後、通常どおり PLOT または EXPORTPDF で PDF 出力すれば SHX 文字が PDF 注釈として埋め込まれます。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="36" customHeight="1">
-      <c r="A9" s="27" t="inlineStr">
-        <is>
-          <t>AutoCAD を終了すると 0 に戻ることがあります。
-運用ルールに含めるか、起動マクロに PDFSHX 1 を入れておくと確実です。</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>その後、通常どおり PLOT または EXPORTPDF で PDF 出力。
+AutoCAD を終了すると 0 に戻ることがあるため、起動マクロに PDFSHX 1 を入れておくと確実。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">  STEP 2　文字スタイルを TrueType に置換（恒久対処／新規物件推奨）</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="88" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>1. STYLE コマンド → 文字スタイル管理ダイアログ
 2. 使用中スタイルを選択 → 「フォント名」を .shx ではなく TrueType（MSゴシック等）に変更
@@ -2141,90 +2209,25 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>✅ TrueType ならどの経路で PDF 化しても文字が保持されます。
-（AutoCAD 直接 / DocuWorks 経由 / CubePDF / Adobe PDF プリンタ 等）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  STEP ⓘ　バージョン別の推奨ルート</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="B16" s="34" t="inlineStr">
-        <is>
-          <t>AutoCAD バージョン</t>
-        </is>
-      </c>
-      <c r="G16" s="34" t="inlineStr">
-        <is>
-          <t>推奨ルート</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="B17" s="35" t="inlineStr">
-        <is>
-          <t>2017〜2023</t>
-        </is>
-      </c>
-      <c r="G17" s="12" t="inlineStr">
-        <is>
-          <t>解決策1 (PDFSHX 1) または EXPORTPDF オプション</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="B18" s="35" t="inlineStr">
-        <is>
-          <t>2024 以降</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>解決策1 (PDFSHX 2) が理想（実テキスト埋め込み）</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="B19" s="35" t="inlineStr">
-        <is>
-          <t>AutoCAD LT</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>PDFSHX 非対応のことが多い → 解決策2 (TrueType 置換) 推奨</t>
+（AutoCAD 直接 ／ DocuWorks 経由 ／ CubePDF ／ Adobe PDF プリンタ 等）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="G19:L19"/>
-    <mergeCell ref="B16:F16"/>
+  <mergeCells count="9">
+    <mergeCell ref="A10:L10"/>
+    <mergeCell ref="A11:L11"/>
     <mergeCell ref="B7:L7"/>
-    <mergeCell ref="G18:L18"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="A12:L12"/>
+    <mergeCell ref="A1:L1"/>
     <mergeCell ref="A5:L5"/>
     <mergeCell ref="A8:L8"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="G16:L16"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="A13:L13"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A15:L15"/>
-    <mergeCell ref="A11:L11"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="G17:L17"/>
     <mergeCell ref="A6:L6"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A12:L12"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.5" footer="0.5"/>
